--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -141,7 +141,7 @@
     <t>Month:</t>
   </si>
   <si>
-    <t>September</t>
+    <t>August-September</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -198,7 +198,13 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
+    <t>Attend all theory lectures and lab sessions"</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Good focus during evening self-study session</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1613,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" ht="41.4" spans="1:14">
+    <row r="6" ht="27.6" spans="1:14">
       <c r="A6" s="6">
         <v>46282</v>
       </c>
@@ -1653,27 +1659,51 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="13" t="str">
+    <row r="7" ht="28.8" spans="1:14">
+      <c r="A7" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B7" s="12">
+        <v>400</v>
+      </c>
+      <c r="C7" s="12">
+        <v>30</v>
+      </c>
+      <c r="D7" s="12">
+        <v>180</v>
+      </c>
+      <c r="E7" s="12">
+        <v>120</v>
+      </c>
+      <c r="F7" s="12">
+        <v>300</v>
+      </c>
+      <c r="G7" s="12">
+        <v>6</v>
+      </c>
+      <c r="H7" s="12">
+        <v>50</v>
+      </c>
+      <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="13" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J7" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="15"/>
+        <v>360</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="11"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,6 +205,39 @@
   </si>
   <si>
     <t>Good focus during evening self-study session</t>
+  </si>
+  <si>
+    <t>worked on C++ OOPs concepts and class assignments</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Attend all lectures; practiced python syntax and loop problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self study </t>
+  </si>
+  <si>
+    <t>Covered DBMS SQL queries and normalization theory</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>sunday self-study; revised computer Network OSI layers</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>long college day; prepared notes for communication skills</t>
+  </si>
+  <si>
+    <t>solved Analytical skills aptitude questions and python functions</t>
+  </si>
+  <si>
+    <t>practised C++ pointers lab exercise and DBMS joins</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1563,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="3">
-        <v>12317423</v>
+        <v>12617423</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -1705,181 +1738,372 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="13" t="str">
+    <row r="8" ht="28.8" spans="1:14">
+      <c r="A8" s="11">
+        <v>46284</v>
+      </c>
+      <c r="B8" s="12">
+        <v>450</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45</v>
+      </c>
+      <c r="D8" s="12">
+        <v>160</v>
+      </c>
+      <c r="E8" s="12">
+        <v>90</v>
+      </c>
+      <c r="F8" s="12">
+        <v>250</v>
+      </c>
+      <c r="G8" s="12">
+        <v>5</v>
+      </c>
+      <c r="H8" s="12">
+        <v>45</v>
+      </c>
+      <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="13" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J8" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="13" t="str">
+        <v>400</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:14">
+      <c r="A9" s="11">
+        <v>46285</v>
+      </c>
+      <c r="B9" s="12">
+        <v>420</v>
+      </c>
+      <c r="C9" s="12">
+        <v>30</v>
+      </c>
+      <c r="D9" s="12">
+        <v>120</v>
+      </c>
+      <c r="E9" s="12">
+        <v>90</v>
+      </c>
+      <c r="F9" s="12">
+        <v>300</v>
+      </c>
+      <c r="G9" s="12">
+        <v>6</v>
+      </c>
+      <c r="H9" s="12">
+        <v>60</v>
+      </c>
+      <c r="I9" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="13" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J9" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="15"/>
+        <v>420</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="13" t="str">
+      <c r="A10" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B10" s="12">
+        <v>410</v>
+      </c>
+      <c r="C10" s="12">
+        <v>40</v>
+      </c>
+      <c r="D10" s="12">
+        <v>90</v>
+      </c>
+      <c r="E10" s="12">
+        <v>120</v>
+      </c>
+      <c r="F10" s="12">
+        <v>250</v>
+      </c>
+      <c r="G10" s="12">
+        <v>3</v>
+      </c>
+      <c r="H10" s="12">
+        <v>45</v>
+      </c>
+      <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="13" t="str">
+        <v>955</v>
+      </c>
+      <c r="J10" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="15"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="13" t="str">
+        <v>485</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:14">
+      <c r="A11" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B11" s="12">
+        <v>480</v>
+      </c>
+      <c r="C11" s="12">
+        <v>30</v>
+      </c>
+      <c r="D11" s="12">
+        <v>150</v>
+      </c>
+      <c r="E11" s="12">
+        <v>60</v>
+      </c>
+      <c r="F11" s="12">
+        <v>300</v>
+      </c>
+      <c r="G11" s="12">
+        <v>4</v>
+      </c>
+      <c r="H11" s="12">
+        <v>60</v>
+      </c>
+      <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="13" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J11" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="13" t="str">
+        <v>360</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:14">
+      <c r="A12" s="11">
+        <v>44827</v>
+      </c>
+      <c r="B12" s="12">
+        <v>420</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>180</v>
+      </c>
+      <c r="E12" s="12">
+        <v>90</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>90</v>
+      </c>
+      <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="13" t="str">
+        <v>780</v>
+      </c>
+      <c r="J12" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="15"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13" t="str">
+        <v>660</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:14">
+      <c r="A13" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B13" s="12">
+        <v>400</v>
+      </c>
+      <c r="C13" s="12">
+        <v>30</v>
+      </c>
+      <c r="D13" s="12">
+        <v>120</v>
+      </c>
+      <c r="E13" s="12">
+        <v>90</v>
+      </c>
+      <c r="F13" s="12">
+        <v>300</v>
+      </c>
+      <c r="G13" s="12">
+        <v>6</v>
+      </c>
+      <c r="H13" s="12">
+        <v>50</v>
+      </c>
+      <c r="I13" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="13" t="str">
+        <v>990</v>
+      </c>
+      <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="15"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13" t="str">
+        <v>450</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:14">
+      <c r="A14" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B14" s="12">
+        <v>420</v>
+      </c>
+      <c r="C14" s="12">
+        <v>40</v>
+      </c>
+      <c r="D14" s="12">
+        <v>100</v>
+      </c>
+      <c r="E14" s="12">
+        <v>120</v>
+      </c>
+      <c r="F14" s="12">
+        <v>250</v>
+      </c>
+      <c r="G14" s="12">
+        <v>5</v>
+      </c>
+      <c r="H14" s="12">
+        <v>60</v>
+      </c>
+      <c r="I14" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="13" t="str">
+        <v>990</v>
+      </c>
+      <c r="J14" s="13">
+        <v>450</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" ht="28.8" spans="1:14">
+      <c r="A15" s="11">
+        <v>46291</v>
+      </c>
+      <c r="B15" s="12">
+        <v>450</v>
+      </c>
+      <c r="C15" s="12">
+        <v>30</v>
+      </c>
+      <c r="D15" s="12">
+        <v>120</v>
+      </c>
+      <c r="E15" s="12">
+        <v>90</v>
+      </c>
+      <c r="F15" s="12">
+        <v>300</v>
+      </c>
+      <c r="G15" s="12">
+        <v>3</v>
+      </c>
+      <c r="H15" s="12">
+        <v>40</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="15"/>
+        <v>410</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="11"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,21 @@
   </si>
   <si>
     <t>practised C++ pointers lab exercise and DBMS joins</t>
+  </si>
+  <si>
+    <t>Solved leetcode logic questions using C++ and python</t>
+  </si>
+  <si>
+    <t>Revised Computer Network IP addressing and subnetting</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Group discussion session in communication class</t>
+  </si>
+  <si>
+    <t>sunday test prep; solved Analytical reasoning mock paper</t>
   </si>
 </sst>
 </file>
@@ -1847,7 +1862,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="12">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G10" s="12">
         <v>3</v>
@@ -1857,11 +1872,11 @@
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>955</v>
+        <v>855</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="1"/>
-        <v>485</v>
+        <v>585</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>53</v>
@@ -1893,7 +1908,7 @@
         <v>60</v>
       </c>
       <c r="F11" s="12">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G11" s="12">
         <v>4</v>
@@ -1903,11 +1918,11 @@
       </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>980</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>57</v>
@@ -2076,7 +2091,7 @@
         <v>90</v>
       </c>
       <c r="F15" s="12">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G15" s="12">
         <v>3</v>
@@ -2086,17 +2101,17 @@
       </c>
       <c r="I15" s="13">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>880</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>560</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>53</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M15" s="14" t="s">
         <v>60</v>
@@ -2105,93 +2120,189 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="13" t="str">
+    <row r="16" ht="28.8" spans="1:14">
+      <c r="A16" s="11">
+        <v>46292</v>
+      </c>
+      <c r="B16" s="12">
+        <v>420</v>
+      </c>
+      <c r="C16" s="12">
+        <v>45</v>
+      </c>
+      <c r="D16" s="12">
+        <v>90</v>
+      </c>
+      <c r="E16" s="12">
+        <v>150</v>
+      </c>
+      <c r="F16" s="12">
+        <v>250</v>
+      </c>
+      <c r="G16" s="12">
+        <v>5</v>
+      </c>
+      <c r="H16" s="12">
+        <v>60</v>
+      </c>
+      <c r="I16" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="13" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J16" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="15"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="13" t="str">
+        <v>425</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:14">
+      <c r="A17" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B17" s="12">
+        <v>480</v>
+      </c>
+      <c r="C17" s="12">
+        <v>30</v>
+      </c>
+      <c r="D17" s="12">
+        <v>120</v>
+      </c>
+      <c r="E17" s="12">
+        <v>60</v>
+      </c>
+      <c r="F17" s="12">
+        <v>200</v>
+      </c>
+      <c r="G17" s="12">
+        <v>4</v>
+      </c>
+      <c r="H17" s="12">
+        <v>50</v>
+      </c>
+      <c r="I17" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="13" t="str">
+        <v>940</v>
+      </c>
+      <c r="J17" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="15"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="13" t="str">
+        <v>500</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" ht="28.8" spans="1:14">
+      <c r="A18" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B18" s="12">
+        <v>420</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
+        <v>150</v>
+      </c>
+      <c r="E18" s="12">
+        <v>120</v>
+      </c>
+      <c r="F18" s="12">
+        <v>200</v>
+      </c>
+      <c r="G18" s="12">
+        <v>4</v>
+      </c>
+      <c r="H18" s="12">
+        <v>45</v>
+      </c>
+      <c r="I18" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="13" t="str">
+        <v>935</v>
+      </c>
+      <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="15"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13" t="str">
+        <v>505</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" ht="28.8" spans="1:14">
+      <c r="A19" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B19" s="12">
+        <v>450</v>
+      </c>
+      <c r="C19" s="12">
+        <v>45</v>
+      </c>
+      <c r="D19" s="12">
+        <v>180</v>
+      </c>
+      <c r="E19" s="12">
+        <v>90</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>120</v>
+      </c>
+      <c r="I19" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="13" t="str">
+        <v>885</v>
+      </c>
+      <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="15"/>
+        <v>555</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="11"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>sunday test prep; solved Analytical reasoning mock paper</t>
+  </si>
+  <si>
+    <t>31/09/2026</t>
   </si>
 </sst>
 </file>
@@ -2304,27 +2307,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="13" t="str">
+    <row r="20" ht="28.8" spans="1:14">
+      <c r="A20" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12">
+        <v>400</v>
+      </c>
+      <c r="C20" s="12">
+        <v>40</v>
+      </c>
+      <c r="D20" s="12">
+        <v>120</v>
+      </c>
+      <c r="E20" s="12">
+        <v>120</v>
+      </c>
+      <c r="F20" s="12">
+        <v>200</v>
+      </c>
+      <c r="G20" s="12">
+        <v>4</v>
+      </c>
+      <c r="H20" s="12">
+        <v>100</v>
+      </c>
+      <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="13" t="str">
+        <v>980</v>
+      </c>
+      <c r="J20" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="15"/>
+        <v>460</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="11"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,9 +253,6 @@
   </si>
   <si>
     <t>sunday test prep; solved Analytical reasoning mock paper</t>
-  </si>
-  <si>
-    <t>31/09/2026</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1709,7 @@
     </row>
     <row r="7" ht="28.8" spans="1:14">
       <c r="A7" s="11">
-        <v>46283</v>
+        <v>46247</v>
       </c>
       <c r="B7" s="12">
         <v>400</v>
@@ -1758,7 +1755,7 @@
     </row>
     <row r="8" ht="28.8" spans="1:14">
       <c r="A8" s="11">
-        <v>46284</v>
+        <v>46248</v>
       </c>
       <c r="B8" s="12">
         <v>450</v>
@@ -1804,7 +1801,7 @@
     </row>
     <row r="9" ht="28.8" spans="1:14">
       <c r="A9" s="11">
-        <v>46285</v>
+        <v>46249</v>
       </c>
       <c r="B9" s="12">
         <v>420</v>
@@ -1850,7 +1847,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="11">
-        <v>46286</v>
+        <v>46250</v>
       </c>
       <c r="B10" s="12">
         <v>410</v>
@@ -1896,7 +1893,7 @@
     </row>
     <row r="11" ht="28.8" spans="1:14">
       <c r="A11" s="11">
-        <v>46287</v>
+        <v>46251</v>
       </c>
       <c r="B11" s="12">
         <v>480</v>
@@ -1942,7 +1939,7 @@
     </row>
     <row r="12" ht="28.8" spans="1:14">
       <c r="A12" s="11">
-        <v>44827</v>
+        <v>46252</v>
       </c>
       <c r="B12" s="12">
         <v>420</v>
@@ -1988,7 +1985,7 @@
     </row>
     <row r="13" ht="28.8" spans="1:14">
       <c r="A13" s="11">
-        <v>46289</v>
+        <v>46253</v>
       </c>
       <c r="B13" s="12">
         <v>400</v>
@@ -2034,7 +2031,7 @@
     </row>
     <row r="14" ht="28.8" spans="1:14">
       <c r="A14" s="11">
-        <v>46290</v>
+        <v>46254</v>
       </c>
       <c r="B14" s="12">
         <v>420</v>
@@ -2079,7 +2076,7 @@
     </row>
     <row r="15" ht="28.8" spans="1:14">
       <c r="A15" s="11">
-        <v>46291</v>
+        <v>46255</v>
       </c>
       <c r="B15" s="12">
         <v>450</v>
@@ -2125,7 +2122,7 @@
     </row>
     <row r="16" ht="28.8" spans="1:14">
       <c r="A16" s="11">
-        <v>46292</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="12">
         <v>420</v>
@@ -2171,7 +2168,7 @@
     </row>
     <row r="17" ht="28.8" spans="1:14">
       <c r="A17" s="11">
-        <v>46293</v>
+        <v>46257</v>
       </c>
       <c r="B17" s="12">
         <v>480</v>
@@ -2217,7 +2214,7 @@
     </row>
     <row r="18" ht="28.8" spans="1:14">
       <c r="A18" s="11">
-        <v>46294</v>
+        <v>46258</v>
       </c>
       <c r="B18" s="12">
         <v>420</v>
@@ -2263,7 +2260,7 @@
     </row>
     <row r="19" ht="28.8" spans="1:14">
       <c r="A19" s="11">
-        <v>46295</v>
+        <v>46259</v>
       </c>
       <c r="B19" s="12">
         <v>450</v>
@@ -2308,8 +2305,8 @@
       </c>
     </row>
     <row r="20" ht="28.8" spans="1:14">
-      <c r="A20" s="11" t="s">
-        <v>75</v>
+      <c r="A20" s="11">
+        <v>46260</v>
       </c>
       <c r="B20" s="12">
         <v>400</v>
@@ -2353,115 +2350,235 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13" t="str">
+    <row r="21" ht="28.8" spans="1:14">
+      <c r="A21" s="11">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="12">
+        <v>420</v>
+      </c>
+      <c r="C21" s="12">
+        <v>45</v>
+      </c>
+      <c r="D21" s="12">
+        <v>90</v>
+      </c>
+      <c r="E21" s="12">
+        <v>150</v>
+      </c>
+      <c r="F21" s="12">
+        <v>250</v>
+      </c>
+      <c r="G21" s="12">
+        <v>5</v>
+      </c>
+      <c r="H21" s="12">
+        <v>60</v>
+      </c>
+      <c r="I21" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="13" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J21" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13" t="str">
+        <v>425</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:14">
+      <c r="A22" s="11">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="12">
+        <v>300</v>
+      </c>
+      <c r="C22" s="12">
+        <v>60</v>
+      </c>
+      <c r="D22" s="12">
+        <v>200</v>
+      </c>
+      <c r="E22" s="12">
+        <v>120</v>
+      </c>
+      <c r="F22" s="12">
+        <v>200</v>
+      </c>
+      <c r="G22" s="12">
+        <v>4</v>
+      </c>
+      <c r="H22" s="12">
+        <v>60</v>
+      </c>
+      <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="13" t="str">
+        <v>940</v>
+      </c>
+      <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="15"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="13" t="str">
+        <v>500</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:14">
+      <c r="A23" s="11">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="12">
+        <v>320</v>
+      </c>
+      <c r="C23" s="12">
+        <v>60</v>
+      </c>
+      <c r="D23" s="12">
+        <v>120</v>
+      </c>
+      <c r="E23" s="12">
+        <v>110</v>
+      </c>
+      <c r="F23" s="12">
+        <v>150</v>
+      </c>
+      <c r="G23" s="12">
+        <v>3</v>
+      </c>
+      <c r="H23" s="12">
+        <v>120</v>
+      </c>
+      <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="13" t="str">
+        <v>880</v>
+      </c>
+      <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13" t="str">
+        <v>560</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:14">
+      <c r="A24" s="11">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="12">
+        <v>350</v>
+      </c>
+      <c r="C24" s="12">
+        <v>50</v>
+      </c>
+      <c r="D24" s="12">
+        <v>180</v>
+      </c>
+      <c r="E24" s="12">
+        <v>80</v>
+      </c>
+      <c r="F24" s="12">
+        <v>400</v>
+      </c>
+      <c r="G24" s="12">
+        <v>8</v>
+      </c>
+      <c r="H24" s="12">
+        <v>50</v>
+      </c>
+      <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="13" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13" t="str">
+        <v>330</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" ht="28.8" spans="1:14">
+      <c r="A25" s="11">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="12">
+        <v>400</v>
+      </c>
+      <c r="C25" s="12">
+        <v>45</v>
+      </c>
+      <c r="D25" s="12">
+        <v>240</v>
+      </c>
+      <c r="E25" s="12">
+        <v>100</v>
+      </c>
+      <c r="F25" s="12">
+        <v>300</v>
+      </c>
+      <c r="G25" s="12">
+        <v>6</v>
+      </c>
+      <c r="H25" s="12">
+        <v>60</v>
+      </c>
+      <c r="I25" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="13" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J25" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="15"/>
+        <v>295</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="11"/>
